--- a/data/meta_analysis/Cat meta-analysis ORs.xlsx
+++ b/data/meta_analysis/Cat meta-analysis ORs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wallacha@qut.edu.au/Documents/Research/Manuscripts/Death Star/Cats vs vertebrates/Datasets/Meta-analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A265F3F-91FD-FC4C-8449-5F50AE6DBE55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A80BC7-4378-4B4F-A622-D4DB4C692F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="78">
   <si>
     <t>scientificName</t>
   </si>
@@ -252,6 +252,21 @@
   </si>
   <si>
     <t>Table S1</t>
+  </si>
+  <si>
+    <t>Inside-outside</t>
+  </si>
+  <si>
+    <t>Inside-outside reproduction</t>
+  </si>
+  <si>
+    <t>unit_of_replication</t>
+  </si>
+  <si>
+    <t>Islands</t>
+  </si>
+  <si>
+    <t>Nests</t>
   </si>
 </sst>
 </file>
@@ -450,7 +465,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -578,6 +593,15 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1710,7 +1734,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11" style="1" customWidth="1"/>
@@ -1735,7 +1759,7 @@
     <col min="22" max="16384" width="8.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>34</v>
       </c>
@@ -1796,8 +1820,11 @@
       <c r="T1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="U1" s="43" t="s">
+        <v>75</v>
+      </c>
     </row>
-    <row r="2" spans="1:20" s="12" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="12" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="5" t="s">
         <v>35</v>
       </c>
@@ -1854,8 +1881,11 @@
       <c r="T2" s="7" t="s">
         <v>16</v>
       </c>
+      <c r="U2" s="44" t="s">
+        <v>76</v>
+      </c>
     </row>
-    <row r="3" spans="1:20" s="20" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" s="20" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="13" t="s">
         <v>36</v>
       </c>
@@ -1912,8 +1942,11 @@
       <c r="T3" s="15" t="s">
         <v>16</v>
       </c>
+      <c r="U3" s="20" t="s">
+        <v>76</v>
+      </c>
     </row>
-    <row r="4" spans="1:20" s="12" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:21" s="12" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="22" t="s">
         <v>37</v>
       </c>
@@ -1970,8 +2003,11 @@
       <c r="T4" s="24" t="s">
         <v>16</v>
       </c>
+      <c r="U4" s="12" t="s">
+        <v>76</v>
+      </c>
     </row>
-    <row r="5" spans="1:20" s="20" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:21" s="20" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
         <v>38</v>
       </c>
@@ -2028,8 +2064,11 @@
       <c r="T5" s="15" t="s">
         <v>16</v>
       </c>
+      <c r="U5" s="20" t="s">
+        <v>76</v>
+      </c>
     </row>
-    <row r="6" spans="1:20" s="12" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:21" s="12" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="22" t="s">
         <v>39</v>
       </c>
@@ -2086,8 +2125,11 @@
       <c r="T6" s="24" t="s">
         <v>16</v>
       </c>
+      <c r="U6" s="12" t="s">
+        <v>76</v>
+      </c>
     </row>
-    <row r="7" spans="1:20" s="20" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:21" s="20" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="13" t="s">
         <v>40</v>
       </c>
@@ -2144,8 +2186,11 @@
       <c r="T7" s="15" t="s">
         <v>16</v>
       </c>
+      <c r="U7" s="20" t="s">
+        <v>76</v>
+      </c>
     </row>
-    <row r="8" spans="1:20" s="41" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:21" s="41" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="35" t="s">
         <v>59</v>
       </c>
@@ -2202,8 +2247,11 @@
       <c r="T8" s="37" t="s">
         <v>16</v>
       </c>
+      <c r="U8" s="41" t="s">
+        <v>76</v>
+      </c>
     </row>
-    <row r="9" spans="1:20" s="20" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:21" s="20" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="13" t="s">
         <v>45</v>
       </c>
@@ -2260,8 +2308,11 @@
       <c r="T9" s="15" t="s">
         <v>52</v>
       </c>
+      <c r="U9" s="45" t="s">
+        <v>77</v>
+      </c>
     </row>
-    <row r="10" spans="1:20" s="20" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:21" s="20" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="42" t="s">
         <v>65</v>
       </c>
@@ -2282,7 +2333,7 @@
         <v>37.859099999999998</v>
       </c>
       <c r="H10" s="30" t="s">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="I10" s="34" t="s">
         <v>57</v>
@@ -2318,10 +2369,13 @@
         <v>51</v>
       </c>
       <c r="T10" s="15" t="s">
-        <v>52</v>
+        <v>74</v>
+      </c>
+      <c r="U10" s="45" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:20" s="12" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:21" s="12" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="32" t="s">
         <v>66</v>
       </c>
@@ -2342,7 +2396,7 @@
         <v>37.859099999999998</v>
       </c>
       <c r="H11" s="28" t="s">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="I11" s="33" t="s">
         <v>58</v>
@@ -2377,8 +2431,11 @@
       <c r="S11" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="T11" s="25" t="s">
-        <v>52</v>
+      <c r="T11" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="U11" s="44" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
